--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>1990519</v>
+      </c>
+      <c r="C2">
+        <v>2025693</v>
+      </c>
+      <c r="D2">
         <v>98.26360657809451</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="C2">
-        <v>309115</v>
+        <v>8810</v>
       </c>
       <c r="D2">
-        <v>354619</v>
+        <v>8872</v>
       </c>
       <c r="E2">
-        <v>87.16820023743793</v>
+        <v>99.30117222723173</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="C3">
-        <v>389234</v>
+        <v>94703</v>
       </c>
       <c r="D3">
-        <v>411392</v>
+        <v>84583</v>
       </c>
       <c r="E3">
-        <v>94.61389623522091</v>
+        <v>111.9645791707554</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +571,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C4">
-        <v>454636</v>
+        <v>121062</v>
       </c>
       <c r="D4">
-        <v>431797</v>
+        <v>120398</v>
       </c>
       <c r="E4">
-        <v>105.2892910325917</v>
+        <v>100.5515041778103</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +592,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C5">
-        <v>492522</v>
+        <v>156367</v>
       </c>
       <c r="D5">
-        <v>491425</v>
+        <v>172664</v>
       </c>
       <c r="E5">
-        <v>100.2232283664852</v>
+        <v>90.56143724227401</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +613,474 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C6">
-        <v>345012</v>
+        <v>204966</v>
       </c>
       <c r="D6">
-        <v>336460</v>
+        <v>225881</v>
       </c>
       <c r="E6">
-        <v>102.5417583070796</v>
+        <v>90.74069974898286</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>214274</v>
+      </c>
+      <c r="D7">
+        <v>188384</v>
+      </c>
+      <c r="E7">
+        <v>113.7432053677595</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Marga Marga</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>386882</v>
+      </c>
+      <c r="D8">
+        <v>392953</v>
+      </c>
+      <c r="E8">
+        <v>98.45503151776421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>803455</v>
+      </c>
+      <c r="D9">
+        <v>831958</v>
+      </c>
+      <c r="E9">
+        <v>96.5739857060092</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>72114</v>
+      </c>
+      <c r="D2">
+        <v>108262</v>
+      </c>
+      <c r="E2">
+        <v>66.6106297685245</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>111349</v>
+      </c>
+      <c r="D3">
+        <v>118148</v>
+      </c>
+      <c r="E3">
+        <v>94.24535328570946</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>125652</v>
+      </c>
+      <c r="D4">
+        <v>128209</v>
+      </c>
+      <c r="E4">
+        <v>98.00560023087303</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>122642</v>
+      </c>
+      <c r="D5">
+        <v>127147</v>
+      </c>
+      <c r="E5">
+        <v>96.45685702375989</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>124944</v>
+      </c>
+      <c r="D6">
+        <v>137358</v>
+      </c>
+      <c r="E6">
+        <v>90.96230288734549</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>141648</v>
+      </c>
+      <c r="D7">
+        <v>146887</v>
+      </c>
+      <c r="E7">
+        <v>96.43331268253827</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>161029</v>
+      </c>
+      <c r="D8">
+        <v>152817</v>
+      </c>
+      <c r="E8">
+        <v>105.3737476851397</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>154424</v>
+      </c>
+      <c r="D9">
+        <v>141694</v>
+      </c>
+      <c r="E9">
+        <v>108.984148940675</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>139183</v>
+      </c>
+      <c r="D10">
+        <v>137286</v>
+      </c>
+      <c r="E10">
+        <v>101.3817869265621</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>122713</v>
+      </c>
+      <c r="D11">
+        <v>127465</v>
+      </c>
+      <c r="E11">
+        <v>96.27191778135175</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>121850</v>
+      </c>
+      <c r="D12">
+        <v>120438</v>
+      </c>
+      <c r="E12">
+        <v>101.1723874524652</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>122481</v>
+      </c>
+      <c r="D13">
+        <v>123823</v>
+      </c>
+      <c r="E13">
+        <v>98.91619489109455</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>125478</v>
+      </c>
+      <c r="D14">
+        <v>119699</v>
+      </c>
+      <c r="E14">
+        <v>104.8279434247571</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>109488</v>
+      </c>
+      <c r="D15">
+        <v>105410</v>
+      </c>
+      <c r="E15">
+        <v>103.8687031590931</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>84329</v>
+      </c>
+      <c r="D16">
+        <v>84557</v>
+      </c>
+      <c r="E16">
+        <v>99.7303594025332</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>63654</v>
+      </c>
+      <c r="D17">
+        <v>61877</v>
+      </c>
+      <c r="E17">
+        <v>102.8718263652084</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>87541</v>
+      </c>
+      <c r="D18">
+        <v>84616</v>
+      </c>
+      <c r="E18">
+        <v>103.4567930415052</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -418,7 +418,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:14</t>
+    <t xml:space="preserve">2026-08-07 07:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -60,16 +60,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_cobertura_2024_valparaiso.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
@@ -621,23 +630,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -660,10 +669,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -677,10 +686,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>983237</v>
@@ -694,10 +703,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1007282</v>
@@ -730,10 +739,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -747,10 +756,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>8810</v>
@@ -764,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>94703</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>121062</v>
@@ -798,10 +807,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>156367</v>
@@ -815,10 +824,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>204966</v>
@@ -832,10 +841,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>214274</v>
@@ -849,10 +858,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>386882</v>
@@ -866,10 +875,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>803455</v>
@@ -902,10 +911,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -919,10 +928,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>72114</v>
@@ -936,10 +945,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>111349</v>
@@ -953,10 +962,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>125652</v>
@@ -970,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>122642</v>
@@ -987,10 +996,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>124944</v>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>141648</v>
@@ -1021,10 +1030,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>161029</v>
@@ -1038,10 +1047,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>154424</v>
@@ -1055,10 +1064,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>139183</v>
@@ -1072,10 +1081,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>122713</v>
@@ -1089,10 +1098,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>121850</v>
@@ -1106,10 +1115,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>122481</v>
@@ -1123,10 +1132,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>125478</v>
@@ -1140,10 +1149,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>109488</v>
@@ -1157,10 +1166,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>84329</v>
@@ -1174,10 +1183,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>63654</v>
@@ -1191,10 +1200,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>87541</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:12</t>
+    <t xml:space="preserve">2026-08-28 11:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:13</t>
+    <t xml:space="preserve">2026-09-01 13:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:22</t>
+    <t xml:space="preserve">2026-09-06 17:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_valparaiso.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:19</t>
+    <t xml:space="preserve">2026-09-08 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
